--- a/performance.xlsx
+++ b/performance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.91.128\dev\cpp-ipc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutouyun\Documents\Works\Develop\cpp-ipc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C4D612-C00D-43A8-8A5F-6382AD094D36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FAFB8E-B42C-4FA2-9B77-27F6CAC7029B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ipc" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>ipc::route</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,14 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PROD-CONS: 1-N: DATAS: Random 2-256 bytes * 100000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PROD-CONS: 1-N/N-1/N-N: DATAS: Random 2-256 bytes * 100000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MSVC 2017 15.9.9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -138,10 +130,6 @@
   </si>
   <si>
     <t>tc_alloc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PROD-CONS: 1-N: DATAS: 8 bytes * 10000000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -182,12 +170,375 @@
     <t>256 - 512 bytes * 2097152</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>PROD-CONS: 1-N, DATAS: 8 bytes * 10000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROD-CONS: 1-N, DATAS: Random 2-256 bytes * 100000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROD-CONS: 1-N/N-1/N-N, DATAS: Random 2-256 bytes * 100000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图示说明：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>横轴为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>参与工作的线程数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>PROD-CONS: 1-N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，意为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生产者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>消费者，其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的个数为参与工作的线程个数</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>纵轴为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每个数据包所需时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>us/d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>表示时间单位为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>us</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>DATAS: Random 2-256 bytes * 100000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，意为每个数据包为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>2-256bytes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>范围内的随机值，一共传输</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>100000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个这样的数据包</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>RTT: 243.364 ms, 2.43364 us/d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，表示数据全部传输完毕，总耗时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>243.364ms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，由于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATAS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总个数为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>100000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个，因此单个数据包耗时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>2.43364us</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,6 +559,13 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -242,11 +600,29 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -256,7 +632,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -268,9 +644,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -288,6 +661,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -332,7 +711,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$K$9</c:f>
+              <c:f>ipc!$K$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -355,7 +734,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$K$11:$K$26</c:f>
+              <c:f>ipc!$K$17:$K$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -422,7 +801,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$M$9</c:f>
+              <c:f>ipc!$M$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -445,7 +824,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$M$11:$M$26</c:f>
+              <c:f>ipc!$M$17:$M$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -2787,7 +3166,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$K$30</c:f>
+              <c:f>ipc!$K$36</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2810,7 +3189,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$K$32:$K$47</c:f>
+              <c:f>ipc!$K$38:$K$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -2877,7 +3256,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$M$30</c:f>
+              <c:f>ipc!$M$36</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2900,7 +3279,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$M$32:$M$47</c:f>
+              <c:f>ipc!$M$38:$M$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -3182,7 +3561,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$K$51</c:f>
+              <c:f>ipc!$K$57</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3205,7 +3584,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$K$53:$K$68</c:f>
+              <c:f>ipc!$K$59:$K$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -3272,7 +3651,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$O$51</c:f>
+              <c:f>ipc!$O$57</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3295,7 +3674,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$O$53:$O$68</c:f>
+              <c:f>ipc!$O$59:$O$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -3577,7 +3956,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$L$51</c:f>
+              <c:f>ipc!$L$57</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3600,7 +3979,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$L$53:$L$68</c:f>
+              <c:f>ipc!$L$59:$L$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -3667,7 +4046,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$P$51</c:f>
+              <c:f>ipc!$P$57</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3690,7 +4069,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$P$53:$P$68</c:f>
+              <c:f>ipc!$P$59:$P$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -3972,7 +4351,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$M$51</c:f>
+              <c:f>ipc!$M$57</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4009,7 +4388,7 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$M$53:$M$68</c:f>
+              <c:f>ipc!$M$59:$M$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -4076,7 +4455,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ipc!$Q$51</c:f>
+              <c:f>ipc!$Q$57</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4113,7 +4492,7 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>ipc!$Q$53:$Q$68</c:f>
+              <c:f>ipc!$Q$59:$Q$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -13664,13 +14043,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13702,13 +14081,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13740,13 +14119,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13778,13 +14157,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13816,13 +14195,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14425,757 +14804,849 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Q96"/>
+  <dimension ref="A2:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="10.625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="6"/>
+    <col min="2" max="2" width="10.625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B3" s="4" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B4" s="4" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B5" s="4" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B6" s="4" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B14" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" s="6">
+        <v>9.0239700000000006E-2</v>
+      </c>
+      <c r="M17" s="6">
+        <v>4.94362E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K18" s="6">
+        <v>0.117628</v>
+      </c>
+      <c r="M18" s="6">
+        <v>6.7011200000000007E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K19" s="6">
+        <v>0.119631</v>
+      </c>
+      <c r="M19" s="6">
+        <v>8.4845699999999996E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K20" s="6">
+        <v>0.121771</v>
+      </c>
+      <c r="M20" s="6">
+        <v>0.10240200000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K21" s="6">
+        <v>0.121962</v>
+      </c>
+      <c r="M21" s="6">
+        <v>0.121748</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K22" s="6">
+        <v>0.135294</v>
+      </c>
+      <c r="M22" s="6">
+        <v>0.13891200000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K23" s="6">
+        <v>0.13072300000000001</v>
+      </c>
+      <c r="M23" s="6">
+        <v>0.15601300000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K24" s="6">
+        <v>0.15015500000000001</v>
+      </c>
+      <c r="M24" s="6">
+        <v>0.174206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K25" s="6">
+        <v>0.153367</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0.19270399999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K26" s="6">
+        <v>0.15768599999999999</v>
+      </c>
+      <c r="M26" s="6">
+        <v>0.20810500000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K27" s="6">
+        <v>0.160936</v>
+      </c>
+      <c r="M27" s="6">
+        <v>0.22763700000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="J28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0.18023500000000001</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0.246616</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K29" s="6">
+        <v>0.18453</v>
+      </c>
+      <c r="M29" s="6">
+        <v>0.26141500000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K30" s="6">
+        <v>0.18893799999999999</v>
+      </c>
+      <c r="M30" s="6">
+        <v>0.28184700000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K31" s="6">
+        <v>0.191108</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0.29949799999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K32" s="6">
+        <v>0.21331700000000001</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0.31859700000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B34" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B35" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="K36" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M36" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A11" s="3" t="s">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A38" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K11" s="1">
-        <v>9.0239700000000006E-2</v>
-      </c>
-      <c r="M11" s="1">
-        <v>4.94362E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K12" s="1">
-        <v>0.117628</v>
-      </c>
-      <c r="M12" s="1">
-        <v>6.7011200000000007E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K13" s="1">
-        <v>0.119631</v>
-      </c>
-      <c r="M13" s="1">
-        <v>8.4845699999999996E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K14" s="1">
-        <v>0.121771</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0.10240200000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K15" s="1">
-        <v>0.121962</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0.121748</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K16" s="1">
-        <v>0.135294</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0.13891200000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K17" s="1">
-        <v>0.13072300000000001</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0.15601300000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K18" s="1">
-        <v>0.15015500000000001</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0.174206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K19" s="1">
-        <v>0.153367</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0.19270399999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K20" s="1">
-        <v>0.15768599999999999</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0.20810500000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K21" s="1">
-        <v>0.160936</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0.22763700000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J22" s="3" t="s">
+      <c r="K38" s="6">
+        <v>1.4636199999999999</v>
+      </c>
+      <c r="M38" s="6">
+        <v>0.76978999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K39" s="6">
+        <v>4.0579599999999996</v>
+      </c>
+      <c r="M39" s="6">
+        <v>1.0757399999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K40" s="6">
+        <v>1.6480600000000001</v>
+      </c>
+      <c r="M40" s="6">
+        <v>1.4403999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K41" s="6">
+        <v>1.9473800000000001</v>
+      </c>
+      <c r="M41" s="6">
+        <v>1.7591600000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K42" s="6">
+        <v>2.5743399999999999</v>
+      </c>
+      <c r="M42" s="6">
+        <v>1.9542600000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K43" s="6">
+        <v>1.8333900000000001</v>
+      </c>
+      <c r="M43" s="6">
+        <v>2.3799800000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K44" s="6">
+        <v>1.68374</v>
+      </c>
+      <c r="M44" s="6">
+        <v>2.6823999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K45" s="6">
+        <v>2.02901</v>
+      </c>
+      <c r="M45" s="6">
+        <v>2.9781599999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K46" s="6">
+        <v>1.8283499999999999</v>
+      </c>
+      <c r="M46" s="6">
+        <v>3.55355</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K47" s="6">
+        <v>2.8757899999999998</v>
+      </c>
+      <c r="M47" s="6">
+        <v>3.7605</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="K48" s="6">
+        <v>2.1543999999999999</v>
+      </c>
+      <c r="M48" s="6">
+        <v>3.90456</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="2">
-        <v>0.18023500000000001</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0.246616</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K23" s="1">
-        <v>0.18453</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0.26141500000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K24" s="1">
-        <v>0.18893799999999999</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0.28184700000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K25" s="1">
-        <v>0.191108</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0.29949799999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="K26" s="1">
-        <v>0.21331700000000001</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0.31859700000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B30" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K30" s="1" t="s">
+      <c r="K49" s="2">
+        <v>2.4405899999999998</v>
+      </c>
+      <c r="M49" s="6">
+        <v>4.6601699999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K50" s="6">
+        <v>2.6548600000000002</v>
+      </c>
+      <c r="M50" s="6">
+        <v>4.7321499999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K51" s="6">
+        <v>2.93215</v>
+      </c>
+      <c r="M51" s="6">
+        <v>4.8681900000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K52" s="6">
+        <v>3.2696200000000002</v>
+      </c>
+      <c r="M52" s="6">
+        <v>5.5490199999999996</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K53" s="6">
+        <v>3.2780200000000002</v>
+      </c>
+      <c r="M53" s="6">
+        <v>5.6832000000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="B55" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="B56" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="B57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="L57" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O57" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A32" s="3" t="s">
+      <c r="P57" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A59" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K32" s="1">
-        <v>1.4636199999999999</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0.76978999999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K33" s="1">
-        <v>4.0579599999999996</v>
-      </c>
-      <c r="M33" s="1">
-        <v>1.0757399999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K34" s="1">
-        <v>1.6480600000000001</v>
-      </c>
-      <c r="M34" s="1">
-        <v>1.4403999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K35" s="1">
-        <v>1.9473800000000001</v>
-      </c>
-      <c r="M35" s="1">
-        <v>1.7591600000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K36" s="1">
-        <v>2.5743399999999999</v>
-      </c>
-      <c r="M36" s="1">
-        <v>1.9542600000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K37" s="1">
-        <v>1.8333900000000001</v>
-      </c>
-      <c r="M37" s="1">
-        <v>2.3799800000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K38" s="1">
-        <v>1.68374</v>
-      </c>
-      <c r="M38" s="1">
-        <v>2.6823999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K39" s="1">
-        <v>2.02901</v>
-      </c>
-      <c r="M39" s="1">
-        <v>2.9781599999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K40" s="1">
-        <v>1.8283499999999999</v>
-      </c>
-      <c r="M40" s="1">
-        <v>3.55355</v>
-      </c>
-    </row>
-    <row r="41" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K41" s="1">
-        <v>2.8757899999999998</v>
-      </c>
-      <c r="M41" s="1">
-        <v>3.7605</v>
-      </c>
-    </row>
-    <row r="42" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K42" s="1">
-        <v>2.1543999999999999</v>
-      </c>
-      <c r="M42" s="1">
-        <v>3.90456</v>
-      </c>
-    </row>
-    <row r="43" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="J43" s="3" t="s">
+      <c r="K59" s="6">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="L59" s="6">
+        <v>0.89007999999999998</v>
+      </c>
+      <c r="M59" s="6">
+        <v>0.65151999999999999</v>
+      </c>
+      <c r="O59" s="6">
+        <v>0.86968000000000001</v>
+      </c>
+      <c r="P59" s="6">
+        <v>0.72950999999999999</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>0.72850999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K60" s="6">
+        <v>0.84325000000000006</v>
+      </c>
+      <c r="L60" s="6">
+        <v>0.54379999999999995</v>
+      </c>
+      <c r="M60" s="6">
+        <v>0.71571499999999999</v>
+      </c>
+      <c r="O60" s="6">
+        <v>1.16652</v>
+      </c>
+      <c r="P60" s="6">
+        <v>0.73068500000000003</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>1.0838699999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K61" s="6">
+        <v>0.96072999999999997</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0.72145300000000001</v>
+      </c>
+      <c r="M61" s="6">
+        <v>0.87939000000000001</v>
+      </c>
+      <c r="O61" s="6">
+        <v>1.42801</v>
+      </c>
+      <c r="P61" s="6">
+        <v>0.71711000000000003</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>1.3628100000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K62" s="6">
+        <v>1.1567499999999999</v>
+      </c>
+      <c r="L62" s="6">
+        <v>0.75402999999999998</v>
+      </c>
+      <c r="M62" s="6">
+        <v>0.99741299999999999</v>
+      </c>
+      <c r="O62" s="6">
+        <v>1.72299</v>
+      </c>
+      <c r="P62" s="6">
+        <v>0.68970500000000001</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>1.64151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K63" s="6">
+        <v>1.51613</v>
+      </c>
+      <c r="L63" s="6">
+        <v>0.67861800000000005</v>
+      </c>
+      <c r="M63" s="6">
+        <v>1.36541</v>
+      </c>
+      <c r="O63" s="6">
+        <v>2.0834999999999999</v>
+      </c>
+      <c r="P63" s="6">
+        <v>0.730522</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>1.94756</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K64" s="6">
+        <v>1.5160899999999999</v>
+      </c>
+      <c r="L64" s="6">
+        <v>0.63654999999999995</v>
+      </c>
+      <c r="M64" s="6">
+        <v>2.0455899999999998</v>
+      </c>
+      <c r="O64" s="6">
+        <v>2.3506499999999999</v>
+      </c>
+      <c r="P64" s="6">
+        <v>0.73874700000000004</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>2.27888</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K65" s="6">
+        <v>1.4708699999999999</v>
+      </c>
+      <c r="L65" s="6">
+        <v>0.62900699999999998</v>
+      </c>
+      <c r="M65" s="6">
+        <v>1.6194299999999999</v>
+      </c>
+      <c r="O65" s="6">
+        <v>2.8561800000000002</v>
+      </c>
+      <c r="P65" s="6">
+        <v>0.73151600000000006</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>2.9637099999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K66" s="6">
+        <v>2.7063700000000002</v>
+      </c>
+      <c r="L66" s="6">
+        <v>0.63006200000000001</v>
+      </c>
+      <c r="M66" s="6">
+        <v>1.5743</v>
+      </c>
+      <c r="O66" s="6">
+        <v>3.01105</v>
+      </c>
+      <c r="P66" s="6">
+        <v>0.73195600000000005</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>2.9072900000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K67" s="6">
+        <v>4.2711499999999996</v>
+      </c>
+      <c r="L67" s="6">
+        <v>0.65471400000000002</v>
+      </c>
+      <c r="M67" s="6">
+        <v>2.1053600000000001</v>
+      </c>
+      <c r="O67" s="6">
+        <v>3.1971599999999998</v>
+      </c>
+      <c r="P67" s="6">
+        <v>0.73870800000000003</v>
+      </c>
+      <c r="Q67" s="6">
+        <v>3.5570400000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K68" s="6">
+        <v>2.2917200000000002</v>
+      </c>
+      <c r="L68" s="6">
+        <v>0.65112000000000003</v>
+      </c>
+      <c r="M68" s="6">
+        <v>2.2038099999999998</v>
+      </c>
+      <c r="O68" s="6">
+        <v>3.95044</v>
+      </c>
+      <c r="P68" s="6">
+        <v>0.76838600000000001</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>4.4267399999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K69" s="6">
+        <v>2.1402299999999999</v>
+      </c>
+      <c r="L69" s="6">
+        <v>0.623865</v>
+      </c>
+      <c r="M69" s="6">
+        <v>2.2206000000000001</v>
+      </c>
+      <c r="O69" s="6">
+        <v>3.9211900000000002</v>
+      </c>
+      <c r="P69" s="6">
+        <v>0.74316099999999996</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>4.4241599999999996</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="J70" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="2">
-        <v>2.4405899999999998</v>
-      </c>
-      <c r="M43" s="1">
-        <v>4.6601699999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K44" s="1">
-        <v>2.6548600000000002</v>
-      </c>
-      <c r="M44" s="1">
-        <v>4.7321499999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K45" s="1">
-        <v>2.93215</v>
-      </c>
-      <c r="M45" s="1">
-        <v>4.8681900000000002</v>
-      </c>
-    </row>
-    <row r="46" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K46" s="1">
-        <v>3.2696200000000002</v>
-      </c>
-      <c r="M46" s="1">
-        <v>5.5490199999999996</v>
-      </c>
-    </row>
-    <row r="47" spans="10:13" x14ac:dyDescent="0.15">
-      <c r="K47" s="1">
-        <v>3.2780200000000002</v>
-      </c>
-      <c r="M47" s="1">
-        <v>5.6832000000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="B49" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="B50" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="B51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A53" s="3" t="s">
+      <c r="K70" s="6">
+        <v>2.6705999999999999</v>
+      </c>
+      <c r="L70" s="6">
+        <v>0.63315699999999997</v>
+      </c>
+      <c r="M70" s="6">
+        <v>2.2403900000000001</v>
+      </c>
+      <c r="O70" s="6">
+        <v>4.2853300000000001</v>
+      </c>
+      <c r="P70" s="6">
+        <v>0.75832699999999997</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>4.23062</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K71" s="6">
+        <v>2.6630699999999998</v>
+      </c>
+      <c r="L71" s="6">
+        <v>0.62561500000000003</v>
+      </c>
+      <c r="M71" s="6">
+        <v>2.7877900000000002</v>
+      </c>
+      <c r="O71" s="6">
+        <v>4.6421599999999996</v>
+      </c>
+      <c r="P71" s="6">
+        <v>0.80708899999999995</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>4.5084400000000002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K72" s="6">
+        <v>2.9592299999999998</v>
+      </c>
+      <c r="L72" s="6">
+        <v>0.630409</v>
+      </c>
+      <c r="M72" s="6">
+        <v>2.7803900000000001</v>
+      </c>
+      <c r="O72" s="6">
+        <v>4.8470800000000001</v>
+      </c>
+      <c r="P72" s="6">
+        <v>0.74058500000000005</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>4.9230600000000004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K73" s="6">
+        <v>3.3083100000000001</v>
+      </c>
+      <c r="L73" s="6">
+        <v>0.62432100000000001</v>
+      </c>
+      <c r="M73" s="6">
+        <v>2.89608</v>
+      </c>
+      <c r="O73" s="6">
+        <v>5.70364</v>
+      </c>
+      <c r="P73" s="6">
+        <v>0.72351299999999996</v>
+      </c>
+      <c r="Q73" s="6">
+        <v>5.6130800000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="K74" s="6">
+        <v>3.3012100000000002</v>
+      </c>
+      <c r="L74" s="6">
+        <v>0.63016899999999998</v>
+      </c>
+      <c r="M74" s="6">
+        <v>2.9323700000000001</v>
+      </c>
+      <c r="O74" s="6">
+        <v>5.5061400000000003</v>
+      </c>
+      <c r="P74" s="6">
+        <v>0.76061699999999999</v>
+      </c>
+      <c r="Q74" s="6">
+        <v>6.8994</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A75" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K53" s="1">
-        <v>0.67400000000000004</v>
-      </c>
-      <c r="L53" s="1">
-        <v>0.89007999999999998</v>
-      </c>
-      <c r="M53" s="1">
-        <v>0.65151999999999999</v>
-      </c>
-      <c r="O53" s="1">
-        <v>0.86968000000000001</v>
-      </c>
-      <c r="P53" s="1">
-        <v>0.72950999999999999</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>0.72850999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K54" s="1">
-        <v>0.84325000000000006</v>
-      </c>
-      <c r="L54" s="1">
-        <v>0.54379999999999995</v>
-      </c>
-      <c r="M54" s="1">
-        <v>0.71571499999999999</v>
-      </c>
-      <c r="O54" s="1">
-        <v>1.16652</v>
-      </c>
-      <c r="P54" s="1">
-        <v>0.73068500000000003</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>1.0838699999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K55" s="1">
-        <v>0.96072999999999997</v>
-      </c>
-      <c r="L55" s="1">
-        <v>0.72145300000000001</v>
-      </c>
-      <c r="M55" s="1">
-        <v>0.87939000000000001</v>
-      </c>
-      <c r="O55" s="1">
-        <v>1.42801</v>
-      </c>
-      <c r="P55" s="1">
-        <v>0.71711000000000003</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>1.3628100000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K56" s="1">
-        <v>1.1567499999999999</v>
-      </c>
-      <c r="L56" s="1">
-        <v>0.75402999999999998</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0.99741299999999999</v>
-      </c>
-      <c r="O56" s="1">
-        <v>1.72299</v>
-      </c>
-      <c r="P56" s="1">
-        <v>0.68970500000000001</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>1.64151</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K57" s="1">
-        <v>1.51613</v>
-      </c>
-      <c r="L57" s="1">
-        <v>0.67861800000000005</v>
-      </c>
-      <c r="M57" s="1">
-        <v>1.36541</v>
-      </c>
-      <c r="O57" s="1">
-        <v>2.0834999999999999</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0.730522</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>1.94756</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K58" s="1">
-        <v>1.5160899999999999</v>
-      </c>
-      <c r="L58" s="1">
-        <v>0.63654999999999995</v>
-      </c>
-      <c r="M58" s="1">
-        <v>2.0455899999999998</v>
-      </c>
-      <c r="O58" s="1">
-        <v>2.3506499999999999</v>
-      </c>
-      <c r="P58" s="1">
-        <v>0.73874700000000004</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>2.27888</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K59" s="1">
-        <v>1.4708699999999999</v>
-      </c>
-      <c r="L59" s="1">
-        <v>0.62900699999999998</v>
-      </c>
-      <c r="M59" s="1">
-        <v>1.6194299999999999</v>
-      </c>
-      <c r="O59" s="1">
-        <v>2.8561800000000002</v>
-      </c>
-      <c r="P59" s="1">
-        <v>0.73151600000000006</v>
-      </c>
-      <c r="Q59" s="1">
-        <v>2.9637099999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K60" s="1">
-        <v>2.7063700000000002</v>
-      </c>
-      <c r="L60" s="1">
-        <v>0.63006200000000001</v>
-      </c>
-      <c r="M60" s="1">
-        <v>1.5743</v>
-      </c>
-      <c r="O60" s="1">
-        <v>3.01105</v>
-      </c>
-      <c r="P60" s="1">
-        <v>0.73195600000000005</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>2.9072900000000002</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K61" s="1">
-        <v>4.2711499999999996</v>
-      </c>
-      <c r="L61" s="1">
-        <v>0.65471400000000002</v>
-      </c>
-      <c r="M61" s="1">
-        <v>2.1053600000000001</v>
-      </c>
-      <c r="O61" s="1">
-        <v>3.1971599999999998</v>
-      </c>
-      <c r="P61" s="1">
-        <v>0.73870800000000003</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>3.5570400000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K62" s="1">
-        <v>2.2917200000000002</v>
-      </c>
-      <c r="L62" s="1">
-        <v>0.65112000000000003</v>
-      </c>
-      <c r="M62" s="1">
-        <v>2.2038099999999998</v>
-      </c>
-      <c r="O62" s="1">
-        <v>3.95044</v>
-      </c>
-      <c r="P62" s="1">
-        <v>0.76838600000000001</v>
-      </c>
-      <c r="Q62" s="1">
-        <v>4.4267399999999997</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K63" s="1">
-        <v>2.1402299999999999</v>
-      </c>
-      <c r="L63" s="1">
-        <v>0.623865</v>
-      </c>
-      <c r="M63" s="1">
-        <v>2.2206000000000001</v>
-      </c>
-      <c r="O63" s="1">
-        <v>3.9211900000000002</v>
-      </c>
-      <c r="P63" s="1">
-        <v>0.74316099999999996</v>
-      </c>
-      <c r="Q63" s="1">
-        <v>4.4241599999999996</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="J64" s="3" t="s">
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="J86" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K64" s="1">
-        <v>2.6705999999999999</v>
-      </c>
-      <c r="L64" s="1">
-        <v>0.63315699999999997</v>
-      </c>
-      <c r="M64" s="1">
-        <v>2.2403900000000001</v>
-      </c>
-      <c r="O64" s="1">
-        <v>4.2853300000000001</v>
-      </c>
-      <c r="P64" s="1">
-        <v>0.75832699999999997</v>
-      </c>
-      <c r="Q64" s="1">
-        <v>4.23062</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K65" s="1">
-        <v>2.6630699999999998</v>
-      </c>
-      <c r="L65" s="1">
-        <v>0.62561500000000003</v>
-      </c>
-      <c r="M65" s="1">
-        <v>2.7877900000000002</v>
-      </c>
-      <c r="O65" s="1">
-        <v>4.6421599999999996</v>
-      </c>
-      <c r="P65" s="1">
-        <v>0.80708899999999995</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>4.5084400000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K66" s="1">
-        <v>2.9592299999999998</v>
-      </c>
-      <c r="L66" s="1">
-        <v>0.630409</v>
-      </c>
-      <c r="M66" s="1">
-        <v>2.7803900000000001</v>
-      </c>
-      <c r="O66" s="1">
-        <v>4.8470800000000001</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0.74058500000000005</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>4.9230600000000004</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K67" s="1">
-        <v>3.3083100000000001</v>
-      </c>
-      <c r="L67" s="1">
-        <v>0.62432100000000001</v>
-      </c>
-      <c r="M67" s="1">
-        <v>2.89608</v>
-      </c>
-      <c r="O67" s="1">
-        <v>5.70364</v>
-      </c>
-      <c r="P67" s="1">
-        <v>0.72351299999999996</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>5.6130800000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="K68" s="1">
-        <v>3.3012100000000002</v>
-      </c>
-      <c r="L68" s="1">
-        <v>0.63016899999999998</v>
-      </c>
-      <c r="M68" s="1">
-        <v>2.9323700000000001</v>
-      </c>
-      <c r="O68" s="1">
-        <v>5.5061400000000003</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0.76061699999999999</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>6.8994</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A69" s="3" t="s">
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A91" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="J80" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A85" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="J96" s="3" t="s">
+    <row r="102" spans="10:10" x14ac:dyDescent="0.15">
+      <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -15188,99 +15659,99 @@
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="10.625" style="1" customWidth="1"/>
     <col min="3" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="9" style="10"/>
+    <col min="15" max="15" width="9" style="9"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="B3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="B4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="B5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="B6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="9" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>31</v>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="9" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.15">
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M12" s="1">
         <v>10.541600000000001</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="9">
         <v>17.9376</v>
       </c>
       <c r="Q12" s="1">
@@ -15294,7 +15765,7 @@
       <c r="M13" s="1">
         <v>5.3596599999999999</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="9">
         <v>9.2064299999999992</v>
       </c>
       <c r="Q13" s="1">
@@ -15308,7 +15779,7 @@
       <c r="M14" s="1">
         <v>3.5325299999999999</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <v>5.2313700000000001</v>
       </c>
       <c r="Q14" s="1">
@@ -15322,7 +15793,7 @@
       <c r="M15" s="1">
         <v>2.6282000000000001</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="9">
         <v>4.1915399999999998</v>
       </c>
       <c r="Q15" s="1">
@@ -15336,7 +15807,7 @@
       <c r="M16" s="1">
         <v>2.5251000000000001</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="9">
         <v>4.2234100000000003</v>
       </c>
       <c r="Q16" s="1">
@@ -15350,7 +15821,7 @@
       <c r="M17" s="1">
         <v>2.5264000000000002</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="9">
         <v>4.1966999999999999</v>
       </c>
       <c r="Q17" s="1">
@@ -15364,7 +15835,7 @@
       <c r="M18" s="1">
         <v>2.6773199999999999</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="9">
         <v>4.1783900000000003</v>
       </c>
       <c r="Q18" s="1">
@@ -15378,7 +15849,7 @@
       <c r="M19" s="1">
         <v>2.5134500000000002</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="9">
         <v>3.3681899999999998</v>
       </c>
       <c r="Q19" s="1">
@@ -15388,170 +15859,170 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="2:19" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O27" s="10"/>
-    </row>
-    <row r="28" spans="2:19" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O28" s="10"/>
-    </row>
-    <row r="29" spans="2:19" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O29" s="10"/>
-    </row>
-    <row r="30" spans="2:19" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O30" s="10"/>
-    </row>
-    <row r="31" spans="2:19" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O31" s="10"/>
+    <row r="27" spans="2:19" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O27" s="9"/>
+    </row>
+    <row r="28" spans="2:19" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O28" s="9"/>
+    </row>
+    <row r="29" spans="2:19" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O29" s="9"/>
+    </row>
+    <row r="30" spans="2:19" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O30" s="9"/>
+    </row>
+    <row r="31" spans="2:19" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O31" s="9"/>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.15">
-      <c r="B32" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O33" s="10"/>
-    </row>
-    <row r="34" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M34" s="7">
+      <c r="B32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M34" s="6">
         <v>10.231299999999999</v>
       </c>
-      <c r="O34" s="10">
+      <c r="O34" s="9">
         <v>18.213799999999999</v>
       </c>
-      <c r="Q34" s="7">
+      <c r="Q34" s="6">
         <v>8.7434100000000008</v>
       </c>
     </row>
-    <row r="35" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M35" s="7">
+    <row r="35" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M35" s="6">
         <v>5.2037199999999997</v>
       </c>
-      <c r="O35" s="10">
+      <c r="O35" s="9">
         <v>9.2019199999999994</v>
       </c>
-      <c r="Q35" s="7">
+      <c r="Q35" s="6">
         <v>4.4105299999999996</v>
       </c>
     </row>
-    <row r="36" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M36" s="7">
+    <row r="36" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M36" s="6">
         <v>3.1685599999999998</v>
       </c>
-      <c r="O36" s="10">
+      <c r="O36" s="9">
         <v>5.9444400000000002</v>
       </c>
-      <c r="Q36" s="7">
+      <c r="Q36" s="6">
         <v>2.41486</v>
       </c>
     </row>
-    <row r="37" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M37" s="7">
+    <row r="37" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M37" s="6">
         <v>2.5904500000000001</v>
       </c>
-      <c r="O37" s="10">
+      <c r="O37" s="9">
         <v>4.3105900000000004</v>
       </c>
-      <c r="Q37" s="7">
+      <c r="Q37" s="6">
         <v>1.82796</v>
       </c>
     </row>
-    <row r="38" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M38" s="7">
+    <row r="38" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M38" s="6">
         <v>2.6365400000000001</v>
       </c>
-      <c r="O38" s="10">
+      <c r="O38" s="9">
         <v>4.28071</v>
       </c>
-      <c r="Q38" s="7">
+      <c r="Q38" s="6">
         <v>1.86852</v>
       </c>
     </row>
-    <row r="39" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M39" s="7">
+    <row r="39" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M39" s="6">
         <v>2.4535800000000001</v>
       </c>
-      <c r="O39" s="10">
+      <c r="O39" s="9">
         <v>4.2800799999999999</v>
       </c>
-      <c r="Q39" s="7">
+      <c r="Q39" s="6">
         <v>1.8126800000000001</v>
       </c>
     </row>
-    <row r="40" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M40" s="7">
+    <row r="40" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M40" s="6">
         <v>2.5073300000000001</v>
       </c>
-      <c r="O40" s="10">
+      <c r="O40" s="9">
         <v>4.2952500000000002</v>
       </c>
-      <c r="Q40" s="7">
+      <c r="Q40" s="6">
         <v>1.7874399999999999</v>
       </c>
     </row>
-    <row r="41" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="M41" s="7">
+    <row r="41" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="M41" s="6">
         <v>2.48143</v>
       </c>
-      <c r="O41" s="10">
+      <c r="O41" s="9">
         <v>3.6126200000000002</v>
       </c>
-      <c r="Q41" s="7">
+      <c r="Q41" s="6">
         <v>1.88551</v>
       </c>
     </row>
-    <row r="42" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O42" s="10"/>
-    </row>
-    <row r="43" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O43" s="10"/>
-    </row>
-    <row r="44" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O44" s="10"/>
-    </row>
-    <row r="45" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O45" s="10"/>
-    </row>
-    <row r="46" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O46" s="10"/>
-    </row>
-    <row r="47" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O47" s="10"/>
-    </row>
-    <row r="48" spans="13:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O48" s="10"/>
-    </row>
-    <row r="49" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O49" s="10"/>
-    </row>
-    <row r="50" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O50" s="10"/>
-    </row>
-    <row r="51" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O51" s="10"/>
-    </row>
-    <row r="52" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O52" s="10"/>
-    </row>
-    <row r="53" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="O53" s="10"/>
-    </row>
-    <row r="55" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M55" s="6" t="s">
+    <row r="42" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O42" s="9"/>
+    </row>
+    <row r="43" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O43" s="9"/>
+    </row>
+    <row r="44" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O44" s="9"/>
+    </row>
+    <row r="45" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O45" s="9"/>
+    </row>
+    <row r="46" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O46" s="9"/>
+    </row>
+    <row r="47" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O47" s="9"/>
+    </row>
+    <row r="48" spans="13:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O48" s="9"/>
+    </row>
+    <row r="49" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O49" s="9"/>
+    </row>
+    <row r="50" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O50" s="9"/>
+    </row>
+    <row r="51" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O51" s="9"/>
+    </row>
+    <row r="52" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O52" s="9"/>
+    </row>
+    <row r="53" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O53" s="9"/>
+    </row>
+    <row r="55" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B55" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="O55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q55" s="6" t="s">
-        <v>31</v>
+      <c r="M55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O55" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B56" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.15">
@@ -15561,7 +16032,7 @@
       <c r="M58" s="1">
         <v>0.126358</v>
       </c>
-      <c r="O58" s="10">
+      <c r="O58" s="9">
         <v>0.104979</v>
       </c>
       <c r="Q58" s="1">
@@ -15572,7 +16043,7 @@
       <c r="M59" s="1">
         <v>0.46383099999999999</v>
       </c>
-      <c r="O59" s="10">
+      <c r="O59" s="9">
         <v>5.2007400000000002E-2</v>
       </c>
       <c r="Q59" s="1">
@@ -15583,7 +16054,7 @@
       <c r="M60" s="1">
         <v>0.43428299999999997</v>
       </c>
-      <c r="O60" s="10">
+      <c r="O60" s="9">
         <v>5.3499499999999998E-2</v>
       </c>
       <c r="Q60" s="1">
@@ -15594,7 +16065,7 @@
       <c r="M61" s="1">
         <v>0.46758499999999997</v>
       </c>
-      <c r="O61" s="10">
+      <c r="O61" s="9">
         <v>4.2333799999999998E-2</v>
       </c>
       <c r="Q61" s="1">
@@ -15605,7 +16076,7 @@
       <c r="M62" s="1">
         <v>0.230075</v>
       </c>
-      <c r="O62" s="10">
+      <c r="O62" s="9">
         <v>4.4232599999999997E-2</v>
       </c>
       <c r="Q62" s="1">
@@ -15616,7 +16087,7 @@
       <c r="M63" s="1">
         <v>0.17593700000000001</v>
       </c>
-      <c r="O63" s="10">
+      <c r="O63" s="9">
         <v>4.5316000000000002E-2</v>
       </c>
       <c r="Q63" s="1">
@@ -15627,7 +16098,7 @@
       <c r="M64" s="1">
         <v>6.2992800000000002E-2</v>
       </c>
-      <c r="O64" s="10">
+      <c r="O64" s="9">
         <v>4.7363500000000003E-2</v>
       </c>
       <c r="Q64" s="1">
@@ -15638,7 +16109,7 @@
       <c r="M65" s="1">
         <v>6.0430999999999999E-2</v>
       </c>
-      <c r="O65" s="10">
+      <c r="O65" s="9">
         <v>3.6313499999999999E-2</v>
       </c>
       <c r="Q65" s="1">
@@ -15650,14 +16121,14 @@
     </row>
     <row r="78" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B78" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="2:17" x14ac:dyDescent="0.15">
       <c r="M80" s="1">
         <v>0.26969900000000002</v>
       </c>
-      <c r="O80" s="10">
+      <c r="O80" s="9">
         <v>0.134765</v>
       </c>
       <c r="Q80" s="1">
@@ -15668,7 +16139,7 @@
       <c r="M81" s="1">
         <v>1.5039199999999999</v>
       </c>
-      <c r="O81" s="10">
+      <c r="O81" s="9">
         <v>7.0637199999999997E-2</v>
       </c>
       <c r="Q81" s="1">
@@ -15679,7 +16150,7 @@
       <c r="M82" s="1">
         <v>2.3091499999999998</v>
       </c>
-      <c r="O82" s="10">
+      <c r="O82" s="9">
         <v>7.4726600000000004E-2</v>
       </c>
       <c r="Q82" s="1">
@@ -15690,7 +16161,7 @@
       <c r="M83" s="1">
         <v>1.8403799999999999</v>
       </c>
-      <c r="O83" s="10">
+      <c r="O83" s="9">
         <v>6.8225900000000006E-2</v>
       </c>
       <c r="Q83" s="1">
@@ -15701,7 +16172,7 @@
       <c r="M84" s="1">
         <v>0.92615199999999998</v>
       </c>
-      <c r="O84" s="10">
+      <c r="O84" s="9">
         <v>3.8167E-2</v>
       </c>
       <c r="Q84" s="1">
@@ -15712,7 +16183,7 @@
       <c r="M85" s="1">
         <v>0.45206600000000002</v>
       </c>
-      <c r="O85" s="10">
+      <c r="O85" s="9">
         <v>5.1627600000000003E-2</v>
       </c>
       <c r="Q85" s="1">
@@ -15723,7 +16194,7 @@
       <c r="M86" s="1">
         <v>0.105153</v>
       </c>
-      <c r="O86" s="10">
+      <c r="O86" s="9">
         <v>4.8516299999999998E-2</v>
       </c>
       <c r="Q86" s="1">
@@ -15734,30 +16205,30 @@
       <c r="M87" s="1">
         <v>5.7405499999999998E-2</v>
       </c>
-      <c r="O87" s="10">
+      <c r="O87" s="9">
         <v>4.0766700000000003E-2</v>
       </c>
       <c r="Q87" s="1">
         <v>5.9599399999999997E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O101" s="10" t="s">
+    <row r="101" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q101" s="6" t="s">
-        <v>31</v>
+      <c r="M101" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O101" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q101" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="B102" s="7" t="s">
-        <v>41</v>
+      <c r="B102" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.15">
@@ -15767,7 +16238,7 @@
       <c r="M104" s="1">
         <v>0.123201</v>
       </c>
-      <c r="O104" s="10">
+      <c r="O104" s="9">
         <v>8.88901E-2</v>
       </c>
       <c r="Q104" s="1">
@@ -15778,7 +16249,7 @@
       <c r="M105" s="1">
         <v>0.15046799999999999</v>
       </c>
-      <c r="O105" s="10">
+      <c r="O105" s="9">
         <v>4.7537599999999999E-2</v>
       </c>
       <c r="Q105" s="1">
@@ -15789,7 +16260,7 @@
       <c r="M106" s="1">
         <v>0.39644800000000002</v>
       </c>
-      <c r="O106" s="10">
+      <c r="O106" s="9">
         <v>3.8765399999999998E-2</v>
       </c>
       <c r="Q106" s="1">
@@ -15800,7 +16271,7 @@
       <c r="M107" s="1">
         <v>0.31692799999999999</v>
       </c>
-      <c r="O107" s="10">
+      <c r="O107" s="9">
         <v>4.0281999999999998E-2</v>
       </c>
       <c r="Q107" s="1">
@@ -15811,7 +16282,7 @@
       <c r="M108" s="1">
         <v>0.12166299999999999</v>
       </c>
-      <c r="O108" s="10">
+      <c r="O108" s="9">
         <v>3.6654899999999997E-2</v>
       </c>
       <c r="Q108" s="1">
@@ -15822,7 +16293,7 @@
       <c r="M109" s="1">
         <v>9.7332500000000002E-2</v>
       </c>
-      <c r="O109" s="10">
+      <c r="O109" s="9">
         <v>3.9388199999999998E-2</v>
       </c>
       <c r="Q109" s="1">
@@ -15833,7 +16304,7 @@
       <c r="M110" s="1">
         <v>7.5878600000000004E-2</v>
       </c>
-      <c r="O110" s="10">
+      <c r="O110" s="9">
         <v>3.4458599999999999E-2</v>
       </c>
       <c r="Q110" s="1">
@@ -15844,7 +16315,7 @@
       <c r="M111" s="1">
         <v>6.6806299999999999E-2</v>
       </c>
-      <c r="O111" s="10">
+      <c r="O111" s="9">
         <v>2.8533200000000002E-2</v>
       </c>
       <c r="Q111" s="1">
@@ -15852,15 +16323,15 @@
       </c>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="B124" s="7" t="s">
-        <v>43</v>
+      <c r="B124" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.15">
       <c r="M126" s="1">
         <v>0.279505</v>
       </c>
-      <c r="O126" s="10">
+      <c r="O126" s="9">
         <v>0.116756</v>
       </c>
       <c r="Q126" s="1">
@@ -15868,11 +16339,11 @@
       </c>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="B127" s="7"/>
+      <c r="B127" s="6"/>
       <c r="M127" s="1">
         <v>1.9100200000000001</v>
       </c>
-      <c r="O127" s="10">
+      <c r="O127" s="9">
         <v>6.7525399999999999E-2</v>
       </c>
       <c r="Q127" s="1">
@@ -15883,7 +16354,7 @@
       <c r="M128" s="1">
         <v>2.1775699999999998</v>
       </c>
-      <c r="O128" s="10">
+      <c r="O128" s="9">
         <v>6.9706000000000004E-2</v>
       </c>
       <c r="Q128" s="1">
@@ -15894,7 +16365,7 @@
       <c r="M129" s="1">
         <v>1.7882800000000001</v>
       </c>
-      <c r="O129" s="10">
+      <c r="O129" s="9">
         <v>8.3218600000000004E-2</v>
       </c>
       <c r="Q129" s="1">
@@ -15905,7 +16376,7 @@
       <c r="M130" s="1">
         <v>0.142404</v>
       </c>
-      <c r="O130" s="10">
+      <c r="O130" s="9">
         <v>9.35111E-2</v>
       </c>
       <c r="Q130" s="1">
@@ -15916,7 +16387,7 @@
       <c r="M131" s="1">
         <v>0.419354</v>
       </c>
-      <c r="O131" s="10">
+      <c r="O131" s="9">
         <v>3.8509399999999999E-2</v>
       </c>
       <c r="Q131" s="1">
@@ -15927,7 +16398,7 @@
       <c r="M132" s="1">
         <v>4.5165999999999998E-2</v>
       </c>
-      <c r="O132" s="10">
+      <c r="O132" s="9">
         <v>3.6715999999999999E-2</v>
       </c>
       <c r="Q132" s="1">
@@ -15938,30 +16409,30 @@
       <c r="M133" s="1">
         <v>4.4523699999999999E-2</v>
       </c>
-      <c r="O133" s="10">
+      <c r="O133" s="9">
         <v>3.3855400000000001E-2</v>
       </c>
       <c r="Q133" s="1">
         <v>7.2250400000000006E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B147" s="6" t="s">
+    <row r="147" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B147" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M147" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O147" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q147" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M147" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q147" s="6" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="B148" s="7" t="s">
-        <v>41</v>
+      <c r="B148" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.15">
@@ -15971,7 +16442,7 @@
       <c r="M150" s="1">
         <v>0.45372000000000001</v>
       </c>
-      <c r="O150" s="10">
+      <c r="O150" s="9">
         <v>0.25519999999999998</v>
       </c>
       <c r="Q150" s="1">
@@ -15982,7 +16453,7 @@
       <c r="M151" s="1">
         <v>0.27060499999999998</v>
       </c>
-      <c r="O151" s="10">
+      <c r="O151" s="9">
         <v>0.147202</v>
       </c>
       <c r="Q151" s="1">
@@ -15993,7 +16464,7 @@
       <c r="M152" s="1">
         <v>0.18004999999999999</v>
       </c>
-      <c r="O152" s="10">
+      <c r="O152" s="9">
         <v>9.2210799999999996E-2</v>
       </c>
       <c r="Q152" s="1">
@@ -16004,7 +16475,7 @@
       <c r="M153" s="1">
         <v>0.14088400000000001</v>
       </c>
-      <c r="O153" s="10">
+      <c r="O153" s="9">
         <v>9.4175099999999998E-2</v>
       </c>
       <c r="Q153" s="1">
@@ -16015,7 +16486,7 @@
       <c r="M154" s="1">
         <v>0.248502</v>
       </c>
-      <c r="O154" s="10">
+      <c r="O154" s="9">
         <v>0.100257</v>
       </c>
       <c r="Q154" s="1">
@@ -16026,7 +16497,7 @@
       <c r="M155" s="1">
         <v>0.17857300000000001</v>
       </c>
-      <c r="O155" s="10">
+      <c r="O155" s="9">
         <v>0.103667</v>
       </c>
       <c r="Q155" s="1">
@@ -16037,7 +16508,7 @@
       <c r="M156" s="1">
         <v>0.12940199999999999</v>
       </c>
-      <c r="O156" s="10">
+      <c r="O156" s="9">
         <v>9.55091E-2</v>
       </c>
       <c r="Q156" s="1">
@@ -16048,7 +16519,7 @@
       <c r="M157" s="1">
         <v>0.111954</v>
       </c>
-      <c r="O157" s="10">
+      <c r="O157" s="9">
         <v>9.1973299999999994E-2</v>
       </c>
       <c r="Q157" s="1">
@@ -16056,15 +16527,15 @@
       </c>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="B170" s="7" t="s">
-        <v>43</v>
+      <c r="B170" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="172" spans="2:17" x14ac:dyDescent="0.15">
       <c r="M172" s="1">
         <v>0.53479399999999999</v>
       </c>
-      <c r="O172" s="10">
+      <c r="O172" s="9">
         <v>0.25068299999999999</v>
       </c>
       <c r="Q172" s="1">
@@ -16072,11 +16543,11 @@
       </c>
     </row>
     <row r="173" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="B173" s="7"/>
+      <c r="B173" s="6"/>
       <c r="M173" s="1">
         <v>0.70010499999999998</v>
       </c>
-      <c r="O173" s="10">
+      <c r="O173" s="9">
         <v>0.15091099999999999</v>
       </c>
       <c r="Q173" s="1">
@@ -16087,7 +16558,7 @@
       <c r="M174" s="1">
         <v>1.4507699999999999</v>
       </c>
-      <c r="O174" s="10">
+      <c r="O174" s="9">
         <v>9.8360500000000003E-2</v>
       </c>
       <c r="Q174" s="1">
@@ -16098,7 +16569,7 @@
       <c r="M175" s="1">
         <v>1.43197</v>
       </c>
-      <c r="O175" s="10">
+      <c r="O175" s="9">
         <v>0.106714</v>
       </c>
       <c r="Q175" s="1">
@@ -16109,7 +16580,7 @@
       <c r="M176" s="1">
         <v>0.42857499999999998</v>
       </c>
-      <c r="O176" s="10">
+      <c r="O176" s="9">
         <v>0.101275</v>
       </c>
       <c r="Q176" s="1">
@@ -16120,7 +16591,7 @@
       <c r="M177" s="1">
         <v>0.12822900000000001</v>
       </c>
-      <c r="O177" s="10">
+      <c r="O177" s="9">
         <v>8.2291100000000006E-2</v>
       </c>
       <c r="Q177" s="1">
@@ -16131,7 +16602,7 @@
       <c r="M178" s="1">
         <v>7.1667700000000001E-2</v>
       </c>
-      <c r="O178" s="10">
+      <c r="O178" s="9">
         <v>9.0575199999999995E-2</v>
       </c>
       <c r="Q178" s="1">
@@ -16142,7 +16613,7 @@
       <c r="M179" s="1">
         <v>7.5734099999999999E-2</v>
       </c>
-      <c r="O179" s="10">
+      <c r="O179" s="9">
         <v>0.11984300000000001</v>
       </c>
       <c r="Q179" s="1">
